--- a/presentaciones.xlsx
+++ b/presentaciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanc\OneDrive\Documentos\LAB-MAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD15A7B-A777-4D2C-9F02-1F9E38C719B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53954AC7-2306-443F-9FCF-B90BEA517F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="107">
   <si>
     <t>Estudiante</t>
   </si>
@@ -347,9 +347,6 @@
     <t>https://arxiv.org/abs/2504.04262</t>
   </si>
   <si>
-    <t>Grupo / Fecha</t>
-  </si>
-  <si>
     <t>26/6</t>
   </si>
   <si>
@@ -359,10 +356,16 @@
     <t>24/6</t>
   </si>
   <si>
-    <t>12/6</t>
-  </si>
-  <si>
-    <t>5/6</t>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPT </t>
+  </si>
+  <si>
+    <t>8/7</t>
+  </si>
+  <si>
+    <t>15/7</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -458,6 +461,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -739,17 +744,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="16.953125" customWidth="1"/>
-    <col min="2" max="3" width="20.1328125" customWidth="1"/>
-    <col min="4" max="4" width="69.2265625" customWidth="1"/>
-    <col min="5" max="5" width="82.54296875" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1328125" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="9.58984375" customWidth="1"/>
+    <col min="5" max="5" width="69.453125" customWidth="1"/>
+    <col min="6" max="6" width="82.54296875" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -757,610 +764,684 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="44.25" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
         <v>102</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
         <v>102</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="44.25" x14ac:dyDescent="0.75">
-      <c r="A16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="44.25" x14ac:dyDescent="0.75">
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="D24" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="7" t="s">
+      <c r="D25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A21" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="D26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="D27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="D28" s="9"/>
+      <c r="E28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A28" t="s">
-        <v>94</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.75">
-      <c r="A29" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="D29" s="9"/>
+      <c r="E29" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G29">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E20" r:id="rId1" xr:uid="{4DBC0373-8C24-EB4C-AA66-4064E1645F09}"/>
-    <hyperlink ref="E8" r:id="rId2" xr:uid="{779D435A-A37E-4505-8CD9-B49F5938BA6C}"/>
-    <hyperlink ref="E2" r:id="rId3" xr:uid="{CD692FFA-FA51-4693-AF71-FB5BAC762DF4}"/>
-    <hyperlink ref="E15" r:id="rId4" xr:uid="{D32D4B97-4949-4A75-9A27-385352E95A71}"/>
-    <hyperlink ref="E9" r:id="rId5" xr:uid="{8780AE28-211A-4BEB-A7D9-1E5BFB2F713D}"/>
-    <hyperlink ref="E6" r:id="rId6" xr:uid="{E5F03273-48E8-4989-88FD-1AD38EB07FF3}"/>
-    <hyperlink ref="E13" r:id="rId7" xr:uid="{4B279132-1C7B-46D3-9084-B82DABA5013B}"/>
-    <hyperlink ref="E10" r:id="rId8" xr:uid="{A0936DE5-7191-4307-BAC1-C965648B204E}"/>
-    <hyperlink ref="E17" r:id="rId9" xr:uid="{CE5A6B3F-DB79-4655-91A1-27AE601C1A55}"/>
-    <hyperlink ref="E16" r:id="rId10" xr:uid="{009D7F3F-0745-41ED-9849-0F1E1D80C3A7}"/>
-    <hyperlink ref="E22" r:id="rId11" location="sec6" xr:uid="{997D29CE-A701-4233-9209-2E2A1C9D1A5F}"/>
-    <hyperlink ref="E23" r:id="rId12" xr:uid="{0DE42600-1C89-409E-94D5-3C426370BB90}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{23E99585-C50F-46AF-9B28-37A3C2A03AF7}"/>
-    <hyperlink ref="E24" r:id="rId14" xr:uid="{8EB81177-508E-AC4F-9034-A684AEE04EEF}"/>
-    <hyperlink ref="E3" r:id="rId15" xr:uid="{41E3E405-D98D-4855-BDAE-6CEA397E4548}"/>
-    <hyperlink ref="E11" r:id="rId16" xr:uid="{FE31BB86-6687-459C-84BE-44E402AC1D44}"/>
-    <hyperlink ref="E12" r:id="rId17" xr:uid="{A6EBA4EA-D826-4D1B-A807-596B25C9D5FF}"/>
-    <hyperlink ref="E25" r:id="rId18" xr:uid="{A074E984-4E20-4E34-A1D3-0DE55B9CDDC1}"/>
-    <hyperlink ref="E4" r:id="rId19" xr:uid="{990B9B42-B33F-4633-825C-6F9835160C60}"/>
-    <hyperlink ref="E27" r:id="rId20" xr:uid="{712692C1-81E2-4243-8719-03749C203648}"/>
-    <hyperlink ref="E26" r:id="rId21" xr:uid="{5588F7BC-1E70-4015-B486-EA6AD5762A3E}"/>
-    <hyperlink ref="E28" r:id="rId22" xr:uid="{19431946-30AA-4CF3-8350-7EBC108EC776}"/>
-    <hyperlink ref="E7" r:id="rId23" xr:uid="{6802D173-6EA9-43DA-85B5-71D7C3E15AC1}"/>
-    <hyperlink ref="E18" r:id="rId24" xr:uid="{2F9974E0-D170-415D-8536-E2554494B17C}"/>
-    <hyperlink ref="E29" r:id="rId25" xr:uid="{E5A5B66D-ABF2-473D-A0CF-B1DD97188281}"/>
-    <hyperlink ref="E21" r:id="rId26" xr:uid="{09AA2B8A-AF20-472B-8AE2-0823280774CD}"/>
-    <hyperlink ref="E5" r:id="rId27" xr:uid="{DF1D14E1-D6A7-45F6-AC5F-6F6F6A726E19}"/>
-    <hyperlink ref="E19" r:id="rId28" xr:uid="{A2534457-280D-460F-A7FC-7942E855493C}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{4DBC0373-8C24-EB4C-AA66-4064E1645F09}"/>
+    <hyperlink ref="F23" r:id="rId2" xr:uid="{779D435A-A37E-4505-8CD9-B49F5938BA6C}"/>
+    <hyperlink ref="F26" r:id="rId3" xr:uid="{CD692FFA-FA51-4693-AF71-FB5BAC762DF4}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{D32D4B97-4949-4A75-9A27-385352E95A71}"/>
+    <hyperlink ref="F22" r:id="rId5" xr:uid="{8780AE28-211A-4BEB-A7D9-1E5BFB2F713D}"/>
+    <hyperlink ref="F27" r:id="rId6" xr:uid="{E5F03273-48E8-4989-88FD-1AD38EB07FF3}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{4B279132-1C7B-46D3-9084-B82DABA5013B}"/>
+    <hyperlink ref="F20" r:id="rId8" xr:uid="{A0936DE5-7191-4307-BAC1-C965648B204E}"/>
+    <hyperlink ref="F9" r:id="rId9" xr:uid="{CE5A6B3F-DB79-4655-91A1-27AE601C1A55}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{009D7F3F-0745-41ED-9849-0F1E1D80C3A7}"/>
+    <hyperlink ref="F4" r:id="rId11" location="sec6" xr:uid="{997D29CE-A701-4233-9209-2E2A1C9D1A5F}"/>
+    <hyperlink ref="F7" r:id="rId12" xr:uid="{0DE42600-1C89-409E-94D5-3C426370BB90}"/>
+    <hyperlink ref="F10" r:id="rId13" xr:uid="{23E99585-C50F-46AF-9B28-37A3C2A03AF7}"/>
+    <hyperlink ref="F16" r:id="rId14" xr:uid="{8EB81177-508E-AC4F-9034-A684AEE04EEF}"/>
+    <hyperlink ref="F25" r:id="rId15" xr:uid="{41E3E405-D98D-4855-BDAE-6CEA397E4548}"/>
+    <hyperlink ref="F19" r:id="rId16" xr:uid="{FE31BB86-6687-459C-84BE-44E402AC1D44}"/>
+    <hyperlink ref="F21" r:id="rId17" xr:uid="{A6EBA4EA-D826-4D1B-A807-596B25C9D5FF}"/>
+    <hyperlink ref="F15" r:id="rId18" xr:uid="{A074E984-4E20-4E34-A1D3-0DE55B9CDDC1}"/>
+    <hyperlink ref="F24" r:id="rId19" xr:uid="{990B9B42-B33F-4633-825C-6F9835160C60}"/>
+    <hyperlink ref="F13" r:id="rId20" xr:uid="{712692C1-81E2-4243-8719-03749C203648}"/>
+    <hyperlink ref="F17" r:id="rId21" xr:uid="{5588F7BC-1E70-4015-B486-EA6AD5762A3E}"/>
+    <hyperlink ref="F18" r:id="rId22" xr:uid="{19431946-30AA-4CF3-8350-7EBC108EC776}"/>
+    <hyperlink ref="F28" r:id="rId23" xr:uid="{6802D173-6EA9-43DA-85B5-71D7C3E15AC1}"/>
+    <hyperlink ref="F5" r:id="rId24" xr:uid="{2F9974E0-D170-415D-8536-E2554494B17C}"/>
+    <hyperlink ref="F14" r:id="rId25" xr:uid="{E5A5B66D-ABF2-473D-A0CF-B1DD97188281}"/>
+    <hyperlink ref="F6" r:id="rId26" xr:uid="{09AA2B8A-AF20-472B-8AE2-0823280774CD}"/>
+    <hyperlink ref="F29" r:id="rId27" xr:uid="{DF1D14E1-D6A7-45F6-AC5F-6F6F6A726E19}"/>
+    <hyperlink ref="F3" r:id="rId28" xr:uid="{A2534457-280D-460F-A7FC-7942E855493C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/presentaciones.xlsx
+++ b/presentaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2f577dda2fcbe77/Documentos/LAB-MAA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B3A7D9-A9C9-4183-84C8-8767C1D8C6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{92B3A7D9-A9C9-4183-84C8-8767C1D8C6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF55DD9-54FB-4A67-B51D-CD9714404E71}"/>
   <bookViews>
-    <workbookView xWindow="1415" yWindow="1415" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="155">
   <si>
     <t>Estudiante</t>
   </si>
@@ -608,26 +607,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -648,6 +638,14 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -966,162 +964,160 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" t="s">
+    <row r="2" spans="1:7" s="6" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="6" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="6" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="6" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="6" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
@@ -1129,45 +1125,45 @@
     </row>
     <row r="9" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>62</v>
+        <v>68</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>51</v>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>77</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
@@ -1175,22 +1171,22 @@
     </row>
     <row r="11" spans="1:7" ht="44.25" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
@@ -1198,411 +1194,415 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="7"/>
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
         <v>64</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F14" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A14" s="11" t="s">
+      <c r="G14" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A15" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="11" t="s">
+      <c r="D15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F15" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A15" s="11" t="s">
+      <c r="G15" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C16" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="11" t="s">
+      <c r="D16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F16" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="11" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A16" s="11" t="s">
+      <c r="G16" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A17" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B17" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C17" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="D17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F17" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A17" s="11" t="s">
+      <c r="G17" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A18" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="11" t="s">
+      <c r="D18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F18" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A18" s="11" t="s">
+      <c r="G18" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A19" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C19" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="11" t="s">
+      <c r="D19" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F19" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A19" s="11" t="s">
+      <c r="G19" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C20" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="D20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="11" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A20" s="11" t="s">
+      <c r="G20" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C21" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="D21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
-      <c r="A21" s="11" t="s">
+      <c r="G21" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C22" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="11" t="s">
+      <c r="D22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F22" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" s="11" t="s">
+      <c r="G22" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C23" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="14" t="s">
+      <c r="D23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="11" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A23" s="11" t="s">
+      <c r="G23" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="6" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C24" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="14" t="s">
+      <c r="D24" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F24" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A24" t="s">
+      <c r="G24" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="D25" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F25" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A25" s="2" t="s">
+      <c r="G25" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A26" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C26" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D26" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F26" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A26" t="s">
+      <c r="G26" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A27" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="D27" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F27" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G27" s="16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A27" t="s">
+    <row r="28" spans="1:7" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C28" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D28" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F28" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A29" t="s">
+      <c r="G28" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A29" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D29" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1614,34 +1614,34 @@
   </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{4DBC0373-8C24-EB4C-AA66-4064E1645F09}"/>
-    <hyperlink ref="F23" r:id="rId2" xr:uid="{779D435A-A37E-4505-8CD9-B49F5938BA6C}"/>
-    <hyperlink ref="F26" r:id="rId3" xr:uid="{CD692FFA-FA51-4693-AF71-FB5BAC762DF4}"/>
-    <hyperlink ref="F8" r:id="rId4" xr:uid="{D32D4B97-4949-4A75-9A27-385352E95A71}"/>
-    <hyperlink ref="F22" r:id="rId5" xr:uid="{8780AE28-211A-4BEB-A7D9-1E5BFB2F713D}"/>
-    <hyperlink ref="F27" r:id="rId6" xr:uid="{E5F03273-48E8-4989-88FD-1AD38EB07FF3}"/>
-    <hyperlink ref="F12" r:id="rId7" xr:uid="{4B279132-1C7B-46D3-9084-B82DABA5013B}"/>
-    <hyperlink ref="F20" r:id="rId8" xr:uid="{A0936DE5-7191-4307-BAC1-C965648B204E}"/>
-    <hyperlink ref="F9" r:id="rId9" xr:uid="{CE5A6B3F-DB79-4655-91A1-27AE601C1A55}"/>
-    <hyperlink ref="F11" r:id="rId10" xr:uid="{009D7F3F-0745-41ED-9849-0F1E1D80C3A7}"/>
-    <hyperlink ref="F4" r:id="rId11" location="sec6" xr:uid="{997D29CE-A701-4233-9209-2E2A1C9D1A5F}"/>
-    <hyperlink ref="F7" r:id="rId12" xr:uid="{0DE42600-1C89-409E-94D5-3C426370BB90}"/>
-    <hyperlink ref="F10" r:id="rId13" xr:uid="{23E99585-C50F-46AF-9B28-37A3C2A03AF7}"/>
-    <hyperlink ref="F16" r:id="rId14" xr:uid="{8EB81177-508E-AC4F-9034-A684AEE04EEF}"/>
-    <hyperlink ref="F25" r:id="rId15" xr:uid="{41E3E405-D98D-4855-BDAE-6CEA397E4548}"/>
-    <hyperlink ref="F19" r:id="rId16" xr:uid="{FE31BB86-6687-459C-84BE-44E402AC1D44}"/>
-    <hyperlink ref="F21" r:id="rId17" xr:uid="{A6EBA4EA-D826-4D1B-A807-596B25C9D5FF}"/>
-    <hyperlink ref="F15" r:id="rId18" xr:uid="{A074E984-4E20-4E34-A1D3-0DE55B9CDDC1}"/>
-    <hyperlink ref="F24" r:id="rId19" xr:uid="{990B9B42-B33F-4633-825C-6F9835160C60}"/>
-    <hyperlink ref="F13" r:id="rId20" xr:uid="{712692C1-81E2-4243-8719-03749C203648}"/>
-    <hyperlink ref="F17" r:id="rId21" xr:uid="{5588F7BC-1E70-4015-B486-EA6AD5762A3E}"/>
-    <hyperlink ref="F18" r:id="rId22" xr:uid="{19431946-30AA-4CF3-8350-7EBC108EC776}"/>
-    <hyperlink ref="F28" r:id="rId23" xr:uid="{6802D173-6EA9-43DA-85B5-71D7C3E15AC1}"/>
-    <hyperlink ref="F5" r:id="rId24" xr:uid="{2F9974E0-D170-415D-8536-E2554494B17C}"/>
-    <hyperlink ref="F14" r:id="rId25" xr:uid="{E5A5B66D-ABF2-473D-A0CF-B1DD97188281}"/>
-    <hyperlink ref="F6" r:id="rId26" xr:uid="{09AA2B8A-AF20-472B-8AE2-0823280774CD}"/>
+    <hyperlink ref="F8" r:id="rId1" xr:uid="{4DBC0373-8C24-EB4C-AA66-4064E1645F09}"/>
+    <hyperlink ref="F24" r:id="rId2" xr:uid="{779D435A-A37E-4505-8CD9-B49F5938BA6C}"/>
+    <hyperlink ref="F27" r:id="rId3" xr:uid="{CD692FFA-FA51-4693-AF71-FB5BAC762DF4}"/>
+    <hyperlink ref="F2" r:id="rId4" xr:uid="{D32D4B97-4949-4A75-9A27-385352E95A71}"/>
+    <hyperlink ref="F23" r:id="rId5" xr:uid="{8780AE28-211A-4BEB-A7D9-1E5BFB2F713D}"/>
+    <hyperlink ref="F28" r:id="rId6" xr:uid="{E5F03273-48E8-4989-88FD-1AD38EB07FF3}"/>
+    <hyperlink ref="F6" r:id="rId7" xr:uid="{4B279132-1C7B-46D3-9084-B82DABA5013B}"/>
+    <hyperlink ref="F21" r:id="rId8" xr:uid="{A0936DE5-7191-4307-BAC1-C965648B204E}"/>
+    <hyperlink ref="F3" r:id="rId9" xr:uid="{CE5A6B3F-DB79-4655-91A1-27AE601C1A55}"/>
+    <hyperlink ref="F5" r:id="rId10" xr:uid="{009D7F3F-0745-41ED-9849-0F1E1D80C3A7}"/>
+    <hyperlink ref="F10" r:id="rId11" location="sec6" xr:uid="{997D29CE-A701-4233-9209-2E2A1C9D1A5F}"/>
+    <hyperlink ref="F13" r:id="rId12" xr:uid="{0DE42600-1C89-409E-94D5-3C426370BB90}"/>
+    <hyperlink ref="F4" r:id="rId13" xr:uid="{23E99585-C50F-46AF-9B28-37A3C2A03AF7}"/>
+    <hyperlink ref="F17" r:id="rId14" xr:uid="{8EB81177-508E-AC4F-9034-A684AEE04EEF}"/>
+    <hyperlink ref="F26" r:id="rId15" xr:uid="{41E3E405-D98D-4855-BDAE-6CEA397E4548}"/>
+    <hyperlink ref="F20" r:id="rId16" xr:uid="{FE31BB86-6687-459C-84BE-44E402AC1D44}"/>
+    <hyperlink ref="F22" r:id="rId17" xr:uid="{A6EBA4EA-D826-4D1B-A807-596B25C9D5FF}"/>
+    <hyperlink ref="F16" r:id="rId18" xr:uid="{A074E984-4E20-4E34-A1D3-0DE55B9CDDC1}"/>
+    <hyperlink ref="F25" r:id="rId19" xr:uid="{990B9B42-B33F-4633-825C-6F9835160C60}"/>
+    <hyperlink ref="F14" r:id="rId20" xr:uid="{712692C1-81E2-4243-8719-03749C203648}"/>
+    <hyperlink ref="F18" r:id="rId21" xr:uid="{5588F7BC-1E70-4015-B486-EA6AD5762A3E}"/>
+    <hyperlink ref="F19" r:id="rId22" xr:uid="{19431946-30AA-4CF3-8350-7EBC108EC776}"/>
+    <hyperlink ref="F7" r:id="rId23" xr:uid="{6802D173-6EA9-43DA-85B5-71D7C3E15AC1}"/>
+    <hyperlink ref="F11" r:id="rId24" xr:uid="{2F9974E0-D170-415D-8536-E2554494B17C}"/>
+    <hyperlink ref="F15" r:id="rId25" xr:uid="{E5A5B66D-ABF2-473D-A0CF-B1DD97188281}"/>
+    <hyperlink ref="F12" r:id="rId26" xr:uid="{09AA2B8A-AF20-472B-8AE2-0823280774CD}"/>
     <hyperlink ref="F29" r:id="rId27" xr:uid="{DF1D14E1-D6A7-45F6-AC5F-6F6F6A726E19}"/>
-    <hyperlink ref="F3" r:id="rId28" xr:uid="{A2534457-280D-460F-A7FC-7942E855493C}"/>
+    <hyperlink ref="F9" r:id="rId28" xr:uid="{A2534457-280D-460F-A7FC-7942E855493C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1669,299 +1669,299 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="12" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="12" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="12" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="26.5" x14ac:dyDescent="0.75">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="12" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="12" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.75">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="12" t="s">
         <v>109</v>
       </c>
     </row>
